--- a/TESTS/zlit_10_odisseya.xlsx
+++ b/TESTS/zlit_10_odisseya.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -557,6 +557,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -599,6 +604,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -641,6 +651,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -683,6 +698,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -725,6 +745,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -767,6 +792,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -809,6 +839,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -851,6 +886,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -893,6 +933,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -935,6 +980,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -977,6 +1027,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1019,6 +1074,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1061,6 +1121,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1103,6 +1168,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1145,6 +1215,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1187,6 +1262,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1229,6 +1309,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1271,6 +1356,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1313,6 +1403,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1355,6 +1450,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1397,6 +1497,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1439,6 +1544,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1481,6 +1591,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1523,6 +1638,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1565,6 +1685,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1607,6 +1732,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1649,6 +1779,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1691,6 +1826,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1733,6 +1873,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1775,6 +1920,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1817,6 +1967,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1831,16 +1986,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1849,6 +2002,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1865,16 +2023,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1883,6 +2039,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1899,16 +2060,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1917,6 +2076,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1928,21 +2092,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Дружина Одіссея Пенелопа чекала його 20 років.</t>
+          <t>Пенелопа чекала Одіссея 20 років: 10 років Троянської війни і 10 років мандрів.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1951,6 +2113,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1962,21 +2129,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Пенелопа вірно чекала Одіссея протягом 20 років.</t>
+          <t>Загалом Одіссей відсутній 20 років: десять воює і десять мандрує назад додому.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1985,6 +2150,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1996,29 +2166,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чи чекала Пенелопа Одіссея 20 років?</t>
+          <t>Пенелопа чекала Одіссея лише три роки.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2030,29 +2203,32 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Одіссей вирізняється насамперед фізичною силою.</t>
+          <t>Одіссей вирізняється насамперед розумом і хитрістю, а не фізичною силою, як-от Ахілл.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>А</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2064,29 +2240,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Головна риса Одіссея — фізична сила, а не розум.</t>
+          <t>Головна риса Одіссея — видатний розум і кмітливість; саме вони рятують його щоразу.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>А</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2098,21 +2277,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Чи є фізична сила головною рисою Одіссея?</t>
+          <t>Головна риса Одіссея — неперевершена фізична сила, а не розум.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Б</t>
@@ -2121,6 +2298,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2165,6 +2347,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2207,6 +2394,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2249,6 +2441,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2291,6 +2488,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2333,6 +2535,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2373,6 +2580,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
